--- a/varia/pathways/progress_overall.xlsx
+++ b/varia/pathways/progress_overall.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t xml:space="preserve">domain</t>
   </si>
@@ -35,10 +35,10 @@
     <t xml:space="preserve">OVERALL</t>
   </si>
   <si>
-    <t xml:space="preserve">39 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34 %</t>
+    <t xml:space="preserve">51 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44 %</t>
   </si>
   <si>
     <t xml:space="preserve">RR</t>
@@ -53,12 +53,15 @@
     <t xml:space="preserve">AR</t>
   </si>
   <si>
+    <t xml:space="preserve">50 %</t>
+  </si>
+  <si>
+    <t xml:space="preserve">summary uncertainty</t>
+  </si>
+  <si>
     <t xml:space="preserve">25 %</t>
   </si>
   <si>
-    <t xml:space="preserve">summary uncertainty</t>
-  </si>
-  <si>
     <t xml:space="preserve">comparison</t>
   </si>
   <si>
@@ -68,15 +71,12 @@
     <t xml:space="preserve">monetization</t>
   </si>
   <si>
-    <t xml:space="preserve">42 %</t>
+    <t xml:space="preserve">75 %</t>
   </si>
   <si>
     <t xml:space="preserve">CBA</t>
   </si>
   <si>
-    <t xml:space="preserve">8 %</t>
-  </si>
-  <si>
     <t xml:space="preserve">DALY</t>
   </si>
   <si>
@@ -86,16 +86,13 @@
     <t xml:space="preserve">socialize</t>
   </si>
   <si>
-    <t xml:space="preserve">12 %</t>
+    <t xml:space="preserve">38 %</t>
   </si>
   <si>
     <t xml:space="preserve">OVERALL (lifetable pathways)</t>
   </si>
   <si>
-    <t xml:space="preserve">31 %</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 %</t>
+    <t xml:space="preserve">5 %</t>
   </si>
   <si>
     <t xml:space="preserve">lifetable</t>
@@ -452,7 +449,7 @@
         <v>6</v>
       </c>
       <c r="B2" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C2" t="s">
         <v>7</v>
@@ -492,7 +489,7 @@
         <v>12</v>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C4" t="s">
         <v>13</v>
@@ -515,10 +512,10 @@
         <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E5" t="n">
         <v>20</v>
@@ -529,16 +526,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B6" t="n">
         <v>8</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E6" t="n">
         <v>8</v>
@@ -549,16 +546,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B7" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D7" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E7" t="n">
         <v>12</v>
@@ -569,16 +566,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="D8" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>12</v>
@@ -595,10 +592,10 @@
         <v>2</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E9" t="n">
         <v>8</v>
@@ -615,10 +612,10 @@
         <v>3</v>
       </c>
       <c r="C10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E10" t="n">
         <v>3</v>
@@ -632,7 +629,7 @@
         <v>23</v>
       </c>
       <c r="B11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11" t="s">
         <v>24</v>
@@ -660,13 +657,13 @@
         <v>25</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="s">
+        <v>24</v>
+      </c>
+      <c r="D13" t="s">
         <v>26</v>
-      </c>
-      <c r="D13" t="s">
-        <v>27</v>
       </c>
       <c r="E13" t="n">
         <v>16</v>
@@ -677,16 +674,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C14" t="s">
+        <v>24</v>
+      </c>
+      <c r="D14" t="s">
         <v>26</v>
-      </c>
-      <c r="D14" t="s">
-        <v>27</v>
       </c>
       <c r="E14" t="n">
         <v>16</v>
